--- a/Inventario de productos Catalogo.xlsx
+++ b/Inventario de productos Catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://silkbancadeinversion-my.sharepoint.com/personal/ysarmiento_rombo_tech/Documents/Escritorio/Iberoamericana/rombo-catalogo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{EBAD1394-F9B9-4433-833D-12DCCBE52741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{258722B8-EEE6-4172-8659-35FA072C0B83}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{EBAD1394-F9B9-4433-833D-12DCCBE52741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C76C2800-AB34-4C58-94FD-AB0477EB0D3F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4A1FC70B-9DE6-46F4-8FC9-1839E09A68A8}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A1FC70B-9DE6-46F4-8FC9-1839E09A68A8}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="72">
   <si>
     <t>Area</t>
   </si>
@@ -689,13 +689,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E41DAF9D-1700-424C-90A0-041EE6134ED8}">
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="79.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.109375" customWidth="1"/>
-    <col min="4" max="4" width="59.44140625" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" customWidth="1"/>
+    <col min="4" max="4" width="22.21875" customWidth="1"/>
     <col min="5" max="5" width="26.21875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -730,7 +730,7 @@
         <v>70</v>
       </c>
       <c r="E2" s="8">
-        <v>1142.1052631578948</v>
+        <v>986</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -744,7 +744,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="8">
-        <v>2121.0526315789475</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -758,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="8">
-        <v>2447.3684210526317</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -772,7 +772,7 @@
         <v>10</v>
       </c>
       <c r="E5" s="8">
-        <v>2594.2105263157896</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -786,7 +786,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="8">
-        <v>3098.3684210526317</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -800,7 +800,7 @@
         <v>14</v>
       </c>
       <c r="E7" s="8">
-        <v>3785.2631578947371</v>
+        <v>3269</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -814,7 +814,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="8">
-        <v>4715.2631578947367</v>
+        <v>4072</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -828,7 +828,7 @@
         <v>18</v>
       </c>
       <c r="E9" s="8">
-        <v>5367.894736842105</v>
+        <v>4636</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -842,7 +842,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="8">
-        <v>5547.3684210526317</v>
+        <v>4791</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -856,7 +856,7 @@
         <v>22</v>
       </c>
       <c r="E11" s="8">
-        <v>5775.7894736842109</v>
+        <v>4988</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -870,7 +870,7 @@
         <v>23</v>
       </c>
       <c r="E12" s="8">
-        <v>6358.2631578947367</v>
+        <v>5491</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -882,7 +882,7 @@
       </c>
       <c r="C13" s="3"/>
       <c r="E13" s="8">
-        <v>2447.3684210526317</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -890,11 +890,11 @@
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C14" s="3"/>
       <c r="E14" s="8">
-        <v>2447.3684210526317</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -902,11 +902,13 @@
         <v>2</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="E15" s="8">
-        <v>326.31578947368422</v>
+        <v>3254</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -914,13 +916,13 @@
         <v>2</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E16" s="8">
-        <v>3767.3157894736842</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -928,13 +930,13 @@
         <v>2</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E17" s="8">
-        <v>326.31578947368422</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -942,13 +944,13 @@
         <v>2</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E18" s="8">
-        <v>358.94736842105266</v>
+        <v>373.63157894736844</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -956,13 +958,13 @@
         <v>2</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E19" s="8">
-        <v>373.63157894736844</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -970,13 +972,13 @@
         <v>2</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="E20" s="8">
-        <v>553.10526315789468</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -984,13 +986,13 @@
         <v>2</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="E21" s="8">
-        <v>5384.2105263157891</v>
+        <v>647</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -998,13 +1000,13 @@
         <v>2</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E22" s="8">
-        <v>748.89473684210532</v>
+        <v>888</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1012,13 +1014,13 @@
         <v>2</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E23" s="8">
-        <v>1027.8947368421052</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1026,13 +1028,13 @@
         <v>2</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E24" s="8">
-        <v>1678.8947368421052</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1040,13 +1042,13 @@
         <v>2</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E25" s="8">
-        <v>4894.7368421052633</v>
+        <v>379</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1054,28 +1056,20 @@
         <v>2</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E26" s="8">
-        <v>438.89473684210526</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1744.1578947368421</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="5"/>
+      <c r="E27" s="8"/>
     </row>
     <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
@@ -1088,7 +1082,7 @@
         <v>28</v>
       </c>
       <c r="E28" s="9">
-        <v>3767.3157894736842</v>
+        <v>3254</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1102,7 +1096,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="9">
-        <v>1142.1052631578948</v>
+        <v>986</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1116,7 +1110,7 @@
         <v>53</v>
       </c>
       <c r="E30" s="9">
-        <v>4274.7368421052633</v>
+        <v>3692</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1130,7 +1124,7 @@
         <v>55</v>
       </c>
       <c r="E31" s="9">
-        <v>8156.2631578947367</v>
+        <v>7044</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1144,7 +1138,7 @@
         <v>57</v>
       </c>
       <c r="E32" s="9">
-        <v>651</v>
+        <v>562</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1158,7 +1152,7 @@
         <v>59</v>
       </c>
       <c r="E33" s="9">
-        <v>3261.5263157894738</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1172,7 +1166,7 @@
         <v>22</v>
       </c>
       <c r="E34" s="9">
-        <v>5775.7894736842109</v>
+        <v>4988</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1184,7 +1178,7 @@
       </c>
       <c r="C35" s="3"/>
       <c r="E35" s="9">
-        <v>2447.3684210526317</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1196,7 +1190,7 @@
       </c>
       <c r="C36" s="3"/>
       <c r="E36" s="9">
-        <v>326.31578947368422</v>
+        <v>282</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1210,7 +1204,7 @@
         <v>18</v>
       </c>
       <c r="E37" s="9">
-        <v>5367.894736842105</v>
+        <v>4636</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1224,7 +1218,7 @@
         <v>46</v>
       </c>
       <c r="E38" s="9">
-        <v>4894.7368421052633</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1238,7 +1232,7 @@
         <v>48</v>
       </c>
       <c r="E39" s="9">
-        <v>438.89473684210526</v>
+        <v>379</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1252,7 +1246,7 @@
         <v>30</v>
       </c>
       <c r="E40" s="9">
-        <v>326.31578947368422</v>
+        <v>282</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1266,7 +1260,7 @@
         <v>36</v>
       </c>
       <c r="E41" s="9">
-        <v>553.10526315789468</v>
+        <v>478</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1280,22 +1274,14 @@
         <v>12</v>
       </c>
       <c r="E42" s="9">
-        <v>3098.3684210526317</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E43" s="9">
-        <v>257.89473684210526</v>
-      </c>
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="5"/>
+      <c r="E43" s="9"/>
     </row>
     <row r="44" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
@@ -1308,7 +1294,7 @@
         <v>4</v>
       </c>
       <c r="E44" s="9">
-        <v>257.89473684210526</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1316,13 +1302,13 @@
         <v>60</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="E45" s="9">
-        <v>965.26315789473688</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1330,13 +1316,13 @@
         <v>60</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E46" s="9">
-        <v>147</v>
+        <v>834</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1344,11 +1330,13 @@
         <v>60</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="3"/>
+        <v>56</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>57</v>
+      </c>
       <c r="E47" s="9">
-        <v>368.4210526315789</v>
+        <v>127</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1356,13 +1344,11 @@
         <v>60</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>59</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C48" s="3"/>
       <c r="E48" s="9">
-        <v>736.47368421052636</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1370,13 +1356,13 @@
         <v>60</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E49" s="9">
-        <v>73.684210526315795</v>
+        <v>636</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1384,13 +1370,13 @@
         <v>60</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E50" s="9">
-        <v>1212.1052631578948</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1398,13 +1384,13 @@
         <v>60</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>46</v>
+        <v>17</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="E51" s="9">
-        <v>1105.2631578947369</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1412,13 +1398,13 @@
         <v>60</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>28</v>
+        <v>45</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="E52" s="9">
-        <v>850.68421052631584</v>
+        <v>955</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1426,13 +1412,13 @@
         <v>60</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="E53" s="9">
-        <v>1435.7368421052631</v>
+        <v>735</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1440,13 +1426,13 @@
         <v>60</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>48</v>
+        <v>25</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="E54" s="9">
-        <v>99.105263157894726</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1454,55 +1440,47 @@
         <v>60</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E55" s="9">
-        <v>124.89473684210526</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E56" s="9">
-        <v>9468.9473684210534</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E57" s="9">
-        <v>3315.7894736842109</v>
-      </c>
+      <c r="A57" s="6"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="E57" s="9"/>
     </row>
     <row r="58" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="E58" s="9">
-        <v>2126.8421052631579</v>
+        <v>8178</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1510,13 +1488,13 @@
         <v>61</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="E59" s="9">
-        <v>1890</v>
+        <v>2864</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1524,13 +1502,13 @@
         <v>61</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="E60" s="9">
-        <v>800.52631578947376</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1538,13 +1516,13 @@
         <v>61</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E61" s="9">
-        <v>800.52631578947376</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1552,13 +1530,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="E62" s="9">
-        <v>14210.526315789473</v>
+        <v>691</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1566,13 +1544,13 @@
         <v>61</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E63" s="9">
-        <v>1274.2105263157894</v>
+        <v>691</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1580,13 +1558,13 @@
         <v>61</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E64" s="9">
-        <v>1605.7894736842104</v>
+        <v>12273</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1594,13 +1572,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="E65" s="9">
-        <v>10937.368421052632</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1608,13 +1586,13 @@
         <v>61</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E66" s="9">
-        <v>947.36842105263167</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1622,69 +1600,61 @@
         <v>61</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E67" s="9">
-        <v>5063.6842105263158</v>
+        <v>9446</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="E68" s="9">
-        <v>1788.5789473684213</v>
+        <v>818</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="E69" s="9">
-        <v>626.31578947368428</v>
+        <v>4373</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E70" s="9">
-        <v>401.73684210526318</v>
-      </c>
+      <c r="A70" s="6"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="E70" s="9"/>
     </row>
     <row r="71" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>66</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E71" s="9">
-        <v>357</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1692,13 +1662,13 @@
         <v>66</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="E72" s="9">
-        <v>151.21052631578948</v>
+        <v>541</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1706,13 +1676,13 @@
         <v>66</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E73" s="9">
-        <v>151.21052631578948</v>
+        <v>347</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1720,13 +1690,13 @@
         <v>66</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E74" s="9">
-        <v>2684.2105263157896</v>
+        <v>308</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1734,13 +1704,13 @@
         <v>66</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E75" s="9">
-        <v>240.68421052631578</v>
+        <v>131</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1748,13 +1718,13 @@
         <v>66</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="E76" s="9">
-        <v>303.31578947368422</v>
+        <v>131</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1762,13 +1732,13 @@
         <v>66</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E77" s="9">
-        <v>2065.9473684210525</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1776,13 +1746,13 @@
         <v>66</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E78" s="9">
-        <v>178.94736842105266</v>
+        <v>208</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1790,13 +1760,55 @@
         <v>66</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E79" s="9">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A80" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E80" s="9">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A81" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E81" s="9">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A82" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E79" s="9">
-        <v>956.47368421052636</v>
+      <c r="E82" s="9">
+        <v>826</v>
       </c>
     </row>
   </sheetData>
@@ -1808,7 +1820,7 @@
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{E40CA847-B4D7-45EC-A3B8-89D2D3D046A9}"/>
-    <hyperlink ref="C21" r:id="rId2" xr:uid="{4EE5776F-3704-4DDB-9ED5-C44C9B832368}"/>
+    <hyperlink ref="C20" r:id="rId2" xr:uid="{4EE5776F-3704-4DDB-9ED5-C44C9B832368}"/>
     <hyperlink ref="C3" r:id="rId3" display="https://www.alkosto.com/secador-gama-viajero-helios-negro/p/8023277149823?algEvent=eyJvYmplY3RJZCI6IjgwMjMyNzcxNDk4MjMiLCJpbmRleCI6ImFsa29zdG9JbmRleEFsZ29saWFQUkRfcHJpY2VfYXNjIiwiYWN0aW9uIjoidmlldyIsInF1ZXJ5SUQiOiJiZTNjZmM3ZDQ0NDUzMWIyNzIyMzVjYjEyNmFmMDQxYyJ9" xr:uid="{3FDB2873-8E6C-4CA7-9723-FB63D978D7E2}"/>
     <hyperlink ref="C30" r:id="rId4" display="https://www.alkosto.com/combo-electrolux-cafetera-ecm25-plancha-sie70/p/7707305812446?algEvent=eyJvYmplY3RJZCI6Ijc3MDczMDU4MTI0NDYiLCJpbmRleCI6ImFsa29zdG9JbmRleEFsZ29saWFQUkRfcHJpY2VfYXNjIiwiYWN0aW9uIjoidmlldyIsInF1ZXJ5SUQiOiI2YTllMzI3ZTZjOTM0YjU1ZjVlMjNmYzZjMjJmOWZmYyJ9" xr:uid="{B274CC32-5F9F-4B2C-BAB5-F6B5CCA20A8F}"/>
     <hyperlink ref="C5" r:id="rId5" xr:uid="{84F15236-08DF-4626-B329-2E6FB824A145}"/>
@@ -1820,26 +1832,26 @@
     <hyperlink ref="C10" r:id="rId11" xr:uid="{94A0462A-2792-4AB1-B217-987DE1651C7C}"/>
     <hyperlink ref="C11" r:id="rId12" display="https://www.alkosto.com/combo-oster-freidora-oster-38-litros-manual-sanduchera/p/7707338078017?algEvent=eyJvYmplY3RJZCI6Ijc3MDczMzgwNzgwMTciLCJpbmRleCI6ImFsa29zdG9JbmRleEFsZ29saWFQUkQiLCJhY3Rpb24iOiJ2aWV3IiwicXVlcnlJRCI6IjYxNzhiNmY4ZjJjNDA2OWEwNTllNDlkNWJiZDVmNmYzIn0=" xr:uid="{E361DE72-602C-4D49-A2DB-3E6CD464836C}"/>
     <hyperlink ref="C12" r:id="rId13" display="https://www.alkosto.com/combo-universal-licuadora-sanduchera-olla-a-presion-6/p/7702561501493?algEvent=eyJvYmplY3RJZCI6Ijc3MDI1NjE1MDE0OTMiLCJpbmRleCI6ImFsa29zdG9JbmRleEFsZ29saWFQUkQiLCJhY3Rpb24iOiJ2aWV3IiwicXVlcnlJRCI6IjAwNjQyN2U3Njc4NWVmMWRkOWU5MzViMTY2Zjk1YjliIn0=" xr:uid="{693D6449-FB7A-4461-B496-E397D543AD4F}"/>
-    <hyperlink ref="C16" r:id="rId14" xr:uid="{D16CC714-27A2-453B-BD65-37B367E17CAE}"/>
-    <hyperlink ref="C17" r:id="rId15" xr:uid="{42951044-7734-4AC5-B8A4-CBC4906179E9}"/>
-    <hyperlink ref="C18" r:id="rId16" display="https://www.alkosto.com/audifonos-esenses-alambricos-in-ear-manos-libres-plug-35/p/7707278179683?algEvent=eyJvYmplY3RJZCI6Ijc3MDcyNzgxNzk2ODMiLCJpbmRleCI6ImFsa29zdG9JbmRleEFsZ29saWFQUkRfcHJpY2VfYXNjIiwiYWN0aW9uIjoidmlldyIsInF1ZXJ5SUQiOiJlNmM3NWJiNzJkMmUwZTg2ZGI0MWY1ODI0N2VjOTM0MSJ9" xr:uid="{E1A456A2-983D-4B54-A346-DBF26D1BB5A5}"/>
-    <hyperlink ref="C19" r:id="rId17" xr:uid="{2E2AF5B5-2AAF-4249-BDB4-7186BE7F989A}"/>
-    <hyperlink ref="C20" r:id="rId18" display="https://www.alkosto.com/mouse-esenses-optico-inalambrico-wom-1010-negro/p/7707278173643?algEvent=eyJvYmplY3RJZCI6Ijc3MDcyNzgxNzM2NDMiLCJpbmRleCI6ImFsa29zdG9JbmRleEFsZ29saWFQUkRfcHJpY2VfYXNjIiwiYWN0aW9uIjoidmlldyIsInF1ZXJ5SUQiOiI5MjFkNTMzYTJmOTk1NzMyOTgyZWE0YzQwODQxOGE5MiJ9" xr:uid="{73C012D0-07C0-4950-8A4E-C155433C76D8}"/>
-    <hyperlink ref="C22" r:id="rId19" xr:uid="{ECB8AC3A-5C0A-453B-A511-F02DEF9ABAE7}"/>
-    <hyperlink ref="C23" r:id="rId20" xr:uid="{C65D9188-59D5-41C0-A9CA-437E6FD9AF46}"/>
-    <hyperlink ref="C24" r:id="rId21" display="https://www.alkosto.com/aspiradora-nano-simoniz-turbo-power-carro/p/7702155088379?algEvent=eyJvYmplY3RJZCI6Ijc3MDIxNTUwODgzNzkiLCJpbmRleCI6ImFsa29zdG9JbmRleEFsZ29saWFQUkRfcHJpY2VfYXNjIiwiYWN0aW9uIjoidmlldyIsInF1ZXJ5SUQiOiJkOTAzYmEwNjA2NDY5ZDNmYThkNmEwOTlhOGE0YmI1YiJ9" xr:uid="{3A47DEFD-4A5F-40A2-87CF-E6A2C3B72C68}"/>
-    <hyperlink ref="C25" r:id="rId22" xr:uid="{A6326F81-D0BF-4C60-A782-62681C1445C1}"/>
-    <hyperlink ref="C26" r:id="rId23" xr:uid="{F9BF16D2-18B2-42C0-9455-09D2881DD2BC}"/>
-    <hyperlink ref="C27" r:id="rId24" xr:uid="{CF9E73FE-A94A-4D94-AA1A-641CB0941900}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{D16CC714-27A2-453B-BD65-37B367E17CAE}"/>
+    <hyperlink ref="C16" r:id="rId15" xr:uid="{42951044-7734-4AC5-B8A4-CBC4906179E9}"/>
+    <hyperlink ref="C17" r:id="rId16" display="https://www.alkosto.com/audifonos-esenses-alambricos-in-ear-manos-libres-plug-35/p/7707278179683?algEvent=eyJvYmplY3RJZCI6Ijc3MDcyNzgxNzk2ODMiLCJpbmRleCI6ImFsa29zdG9JbmRleEFsZ29saWFQUkRfcHJpY2VfYXNjIiwiYWN0aW9uIjoidmlldyIsInF1ZXJ5SUQiOiJlNmM3NWJiNzJkMmUwZTg2ZGI0MWY1ODI0N2VjOTM0MSJ9" xr:uid="{E1A456A2-983D-4B54-A346-DBF26D1BB5A5}"/>
+    <hyperlink ref="C18" r:id="rId17" xr:uid="{2E2AF5B5-2AAF-4249-BDB4-7186BE7F989A}"/>
+    <hyperlink ref="C19" r:id="rId18" display="https://www.alkosto.com/mouse-esenses-optico-inalambrico-wom-1010-negro/p/7707278173643?algEvent=eyJvYmplY3RJZCI6Ijc3MDcyNzgxNzM2NDMiLCJpbmRleCI6ImFsa29zdG9JbmRleEFsZ29saWFQUkRfcHJpY2VfYXNjIiwiYWN0aW9uIjoidmlldyIsInF1ZXJ5SUQiOiI5MjFkNTMzYTJmOTk1NzMyOTgyZWE0YzQwODQxOGE5MiJ9" xr:uid="{73C012D0-07C0-4950-8A4E-C155433C76D8}"/>
+    <hyperlink ref="C21" r:id="rId19" xr:uid="{ECB8AC3A-5C0A-453B-A511-F02DEF9ABAE7}"/>
+    <hyperlink ref="C22" r:id="rId20" xr:uid="{C65D9188-59D5-41C0-A9CA-437E6FD9AF46}"/>
+    <hyperlink ref="C23" r:id="rId21" display="https://www.alkosto.com/aspiradora-nano-simoniz-turbo-power-carro/p/7702155088379?algEvent=eyJvYmplY3RJZCI6Ijc3MDIxNTUwODgzNzkiLCJpbmRleCI6ImFsa29zdG9JbmRleEFsZ29saWFQUkRfcHJpY2VfYXNjIiwiYWN0aW9uIjoidmlldyIsInF1ZXJ5SUQiOiJkOTAzYmEwNjA2NDY5ZDNmYThkNmEwOTlhOGE0YmI1YiJ9" xr:uid="{3A47DEFD-4A5F-40A2-87CF-E6A2C3B72C68}"/>
+    <hyperlink ref="C24" r:id="rId22" xr:uid="{A6326F81-D0BF-4C60-A782-62681C1445C1}"/>
+    <hyperlink ref="C25" r:id="rId23" xr:uid="{F9BF16D2-18B2-42C0-9455-09D2881DD2BC}"/>
+    <hyperlink ref="C26" r:id="rId24" xr:uid="{CF9E73FE-A94A-4D94-AA1A-641CB0941900}"/>
     <hyperlink ref="C28" r:id="rId25" xr:uid="{F126805D-8DB3-4F72-B670-69E91980981C}"/>
     <hyperlink ref="C31" r:id="rId26" display="https://www.alkosto.com/monitor-kalley-22-pulgadas-k-m22fp-fhd-plano-negro/p/7705946476904?algEvent=eyJvYmplY3RJZCI6Ijc3MDU5NDY0NzY5MDQiLCJpbmRleCI6ImFsa29zdG9JbmRleEFsZ29saWFQUkRfcHJpY2VfYXNjIiwiYWN0aW9uIjoidmlldyIsInF1ZXJ5SUQiOiJlN2YwM2Q4NWEyMzQ3Y2ZmN2JlY2Y5ZjEyNDMzOTkyNyJ9" xr:uid="{201A153A-E7B2-4831-9A15-EB7360A83B4C}"/>
     <hyperlink ref="C32" r:id="rId27" display="https://www.alkosto.com/rueda-abdominal-evolution-negra/p/7707118730388?algEvent=eyJvYmplY3RJZCI6Ijc3MDcxMTg3MzAzODgiLCJpbmRleCI6ImFsa29zdG9JbmRleEFsZ29saWFQUkRfcHJpY2VfYXNjIiwiYWN0aW9uIjoidmlldyIsInF1ZXJ5SUQiOiI0OGE0YWQ2YTlkNTQ2Yzg3NGMyMDI0OGQ5NDZlMjhjMSJ9" xr:uid="{261B6B9D-157F-4961-A89C-096C6A9A1F9E}"/>
     <hyperlink ref="C33" r:id="rId28" xr:uid="{7EC91300-8A39-41F6-BD01-E1F07891DC80}"/>
     <hyperlink ref="C34" r:id="rId29" display="https://www.alkosto.com/combo-oster-freidora-oster-38-litros-manual-sanduchera/p/7707338078017?algEvent=eyJvYmplY3RJZCI6Ijc3MDczMzgwNzgwMTciLCJpbmRleCI6ImFsa29zdG9JbmRleEFsZ29saWFQUkQiLCJhY3Rpb24iOiJ2aWV3IiwicXVlcnlJRCI6IjYxNzhiNmY4ZjJjNDA2OWEwNTllNDlkNWJiZDVmNmYzIn0=" xr:uid="{DBD9861E-D8AB-4DA4-94B4-51294B1D778A}"/>
-    <hyperlink ref="C53" r:id="rId30" display="https://www.alkosto.com/combo-universal-licuadora-sanduchera-olla-a-presion-6/p/7702561501493?algEvent=eyJvYmplY3RJZCI6Ijc3MDI1NjE1MDE0OTMiLCJpbmRleCI6ImFsa29zdG9JbmRleEFsZ29saWFQUkQiLCJhY3Rpb24iOiJ2aWV3IiwicXVlcnlJRCI6IjAwNjQyN2U3Njc4NWVmMWRkOWU5MzViMTY2Zjk1YjliIn0=" xr:uid="{AB7E9839-87FD-49EC-8C32-33CAF3CE8E5D}"/>
+    <hyperlink ref="C54" r:id="rId30" display="https://www.alkosto.com/combo-universal-licuadora-sanduchera-olla-a-presion-6/p/7702561501493?algEvent=eyJvYmplY3RJZCI6Ijc3MDI1NjE1MDE0OTMiLCJpbmRleCI6ImFsa29zdG9JbmRleEFsZ29saWFQUkQiLCJhY3Rpb24iOiJ2aWV3IiwicXVlcnlJRCI6IjAwNjQyN2U3Njc4NWVmMWRkOWU5MzViMTY2Zjk1YjliIn0=" xr:uid="{AB7E9839-87FD-49EC-8C32-33CAF3CE8E5D}"/>
     <hyperlink ref="C42" r:id="rId31" xr:uid="{952AE735-0E7A-478A-BF37-7B29487B3B23}"/>
-    <hyperlink ref="C51" r:id="rId32" xr:uid="{261EBBAC-88F7-4E50-9E0A-B48CAE1B0E08}"/>
-    <hyperlink ref="C58" r:id="rId33" display="https://www.alkosto.com/sarten-18-cm-free-home-antiadherente-tipo-marmol-essencial/p/7700149400176?algEvent=eyJvYmplY3RJZCI6Ijc3MDAxNDk0MDAxNzYiLCJpbmRleCI6ImFsa29zdG9JbmRleEFsZ29saWFQUkRfcHJpY2VfYXNjIiwiYWN0aW9uIjoidmlldyIsInF1ZXJ5SUQiOiIyOGFkZTBmNjQ1N2I4MTFjYjQ1MDM5NWUzMzMxZGIwOSJ9" xr:uid="{D49DE644-6E28-4157-AFEE-26574FF50FED}"/>
+    <hyperlink ref="C52" r:id="rId32" xr:uid="{261EBBAC-88F7-4E50-9E0A-B48CAE1B0E08}"/>
+    <hyperlink ref="C60" r:id="rId33" display="https://www.alkosto.com/sarten-18-cm-free-home-antiadherente-tipo-marmol-essencial/p/7700149400176?algEvent=eyJvYmplY3RJZCI6Ijc3MDAxNDk0MDAxNzYiLCJpbmRleCI6ImFsa29zdG9JbmRleEFsZ29saWFQUkRfcHJpY2VfYXNjIiwiYWN0aW9uIjoidmlldyIsInF1ZXJ5SUQiOiIyOGFkZTBmNjQ1N2I4MTFjYjQ1MDM5NWUzMzMxZGIwOSJ9" xr:uid="{D49DE644-6E28-4157-AFEE-26574FF50FED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId34"/>

--- a/Inventario de productos Catalogo.xlsx
+++ b/Inventario de productos Catalogo.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="31" documentId="8_{EBAD1394-F9B9-4433-833D-12DCCBE52741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C76C2800-AB34-4C58-94FD-AB0477EB0D3F}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A1FC70B-9DE6-46F4-8FC9-1839E09A68A8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4A1FC70B-9DE6-46F4-8FC9-1839E09A68A8}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
